--- a/research/traditional_assets/database/data/jordan/jordan_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_insurance_prop_cas.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AQ4"/>
+  <dimension ref="A1:AQ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -579,7 +579,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0112</v>
+        <v>0.0862</v>
       </c>
       <c r="E2">
-        <v>0.0169</v>
+        <v>-0.00335</v>
       </c>
       <c r="G2">
-        <v>0.1042558486809358</v>
+        <v>0.126090407938258</v>
       </c>
       <c r="H2">
-        <v>0.1042558486809358</v>
+        <v>0.126090407938258</v>
       </c>
       <c r="I2">
-        <v>0.1342707814833251</v>
+        <v>0.2077618522601984</v>
       </c>
       <c r="J2">
-        <v>0.1117974305756374</v>
+        <v>0.1610511286222667</v>
       </c>
       <c r="K2">
-        <v>49.42</v>
+        <v>72.52500000000001</v>
       </c>
       <c r="L2">
-        <v>0.1229965156794425</v>
+        <v>0.159922822491731</v>
       </c>
       <c r="M2">
-        <v>13.426</v>
+        <v>20.386</v>
       </c>
       <c r="N2">
-        <v>0.03146472931802203</v>
+        <v>0.04775021666315322</v>
       </c>
       <c r="O2">
-        <v>0.2716713881019829</v>
+        <v>0.2810892795587728</v>
       </c>
       <c r="P2">
-        <v>13.426</v>
+        <v>20.386</v>
       </c>
       <c r="Q2">
-        <v>0.03146472931802203</v>
+        <v>0.04775021666315322</v>
       </c>
       <c r="R2">
-        <v>0.2716713881019829</v>
+        <v>0.2810892795587728</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>228.04</v>
+        <v>256.23</v>
       </c>
       <c r="V2">
-        <v>0.5344269978907897</v>
+        <v>0.60016864591385</v>
       </c>
       <c r="W2">
-        <v>0.1091770105909878</v>
+        <v>0.08456973293768545</v>
       </c>
       <c r="X2">
-        <v>0.08427806289100653</v>
+        <v>0.133594302437083</v>
       </c>
       <c r="Y2">
-        <v>0.0248989476999813</v>
+        <v>-0.04902456949939753</v>
       </c>
       <c r="Z2">
-        <v>4.257709017696302</v>
+        <v>2.158906978958393</v>
       </c>
       <c r="AA2">
-        <v>0.4048190432523695</v>
+        <v>0.09409392801299164</v>
       </c>
       <c r="AB2">
-        <v>0.08427806289100653</v>
+        <v>0.133594302437083</v>
       </c>
       <c r="AC2">
-        <v>0.3205409803613629</v>
+        <v>-0.03950037442409134</v>
       </c>
       <c r="AD2">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG2">
-        <v>-228.04</v>
+        <v>-254.48</v>
       </c>
       <c r="AH2">
-        <v>0</v>
+        <v>0.004082299150881777</v>
       </c>
       <c r="AI2">
-        <v>0</v>
+        <v>0.003943661971830986</v>
       </c>
       <c r="AJ2">
-        <v>-1.147890868821101</v>
+        <v>-1.475674108437228</v>
       </c>
       <c r="AK2">
-        <v>-1.133624975144164</v>
+        <v>-1.357081911262798</v>
       </c>
       <c r="AL2">
-        <v>0.203</v>
+        <v>0.358</v>
       </c>
       <c r="AM2">
-        <v>0.203</v>
+        <v>0.358</v>
       </c>
       <c r="AN2">
-        <v>0</v>
+        <v>0.01823866597186035</v>
       </c>
       <c r="AO2">
-        <v>265.7635467980296</v>
+        <v>263.1843575418994</v>
       </c>
       <c r="AP2">
-        <v>-4.116988626105795</v>
+        <v>-2.652214695153726</v>
       </c>
       <c r="AQ2">
-        <v>265.7635467980296</v>
+        <v>263.1843575418994</v>
       </c>
     </row>
     <row r="3">
@@ -722,40 +722,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.1031207598371778</v>
+        <v>0.1335191284519888</v>
       </c>
       <c r="H3">
-        <v>0.1031207598371778</v>
+        <v>0.1335191284519888</v>
       </c>
       <c r="I3">
-        <v>0.135685210312076</v>
+        <v>0.2259944261464404</v>
       </c>
       <c r="J3">
-        <v>0.1290813084604862</v>
+        <v>0.2235723624974964</v>
       </c>
       <c r="K3">
-        <v>46.6</v>
+        <v>69</v>
       </c>
       <c r="L3">
-        <v>0.1264586160108548</v>
+        <v>0.174816316189511</v>
       </c>
       <c r="M3">
-        <v>11.736</v>
+        <v>18.696</v>
       </c>
       <c r="N3">
-        <v>0.02963636363636363</v>
+        <v>0.04753623188405797</v>
       </c>
       <c r="O3">
-        <v>0.2518454935622317</v>
+        <v>0.2709565217391304</v>
       </c>
       <c r="P3">
-        <v>11.736</v>
+        <v>18.696</v>
       </c>
       <c r="Q3">
-        <v>0.02963636363636363</v>
+        <v>0.04753623188405797</v>
       </c>
       <c r="R3">
-        <v>0.2518454935622317</v>
+        <v>0.2709565217391304</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,31 +764,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>224.4</v>
+        <v>246.7</v>
       </c>
       <c r="V3">
-        <v>0.5666666666666667</v>
+        <v>0.6272565471650139</v>
       </c>
       <c r="W3">
-        <v>0.1227608008429926</v>
+        <v>0.1744627054361568</v>
       </c>
       <c r="X3">
-        <v>0.08427806289100653</v>
+        <v>0.133594302437083</v>
       </c>
       <c r="Y3">
-        <v>0.03848273795198609</v>
+        <v>0.04086840299907379</v>
       </c>
       <c r="Z3">
-        <v>5.45925925925926</v>
+        <v>2.306838106370543</v>
       </c>
       <c r="AA3">
-        <v>0.7046883284102098</v>
+        <v>0.5157452453405134</v>
       </c>
       <c r="AB3">
-        <v>0.08427806289100653</v>
+        <v>0.133594302437083</v>
       </c>
       <c r="AC3">
-        <v>0.6204102655192032</v>
+        <v>0.3821509429034304</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -800,7 +800,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-224.4</v>
+        <v>-246.7</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -809,28 +809,28 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-1.307692307692308</v>
+        <v>-1.682810368349249</v>
       </c>
       <c r="AK3">
-        <v>-1.311513734658095</v>
+        <v>-1.606119791666666</v>
       </c>
       <c r="AL3">
-        <v>0.203</v>
+        <v>0.358</v>
       </c>
       <c r="AM3">
-        <v>0.203</v>
+        <v>0.358</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
       <c r="AO3">
-        <v>246.3054187192118</v>
+        <v>249.1620111731844</v>
       </c>
       <c r="AP3">
-        <v>-4.374269005847953</v>
+        <v>-2.722958057395144</v>
       </c>
       <c r="AQ3">
-        <v>246.3054187192118</v>
+        <v>249.1620111731844</v>
       </c>
     </row>
     <row r="4">
@@ -841,7 +841,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Islamic Insurance Company Plc. (ASE:TIIC)</t>
+          <t>The Islamic Insurance Company (ASE:TIIC)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -850,46 +850,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0112</v>
+        <v>0.0154</v>
       </c>
       <c r="E4">
-        <v>0.0169</v>
+        <v>-0.00335</v>
       </c>
       <c r="G4">
-        <v>0.1168168168168168</v>
+        <v>0.110958904109589</v>
       </c>
       <c r="H4">
-        <v>0.1168168168168168</v>
+        <v>0.110958904109589</v>
       </c>
       <c r="I4">
-        <v>0.1186186186186186</v>
+        <v>0.107945205479452</v>
       </c>
       <c r="J4">
-        <v>0.08468468468468471</v>
+        <v>0.07749215002932956</v>
       </c>
       <c r="K4">
-        <v>2.82</v>
+        <v>2.85</v>
       </c>
       <c r="L4">
-        <v>0.08468468468468469</v>
+        <v>0.07808219178082192</v>
       </c>
       <c r="M4">
         <v>1.69</v>
       </c>
       <c r="N4">
-        <v>0.05504885993485342</v>
+        <v>0.05633333333333333</v>
       </c>
       <c r="O4">
-        <v>0.599290780141844</v>
+        <v>0.5929824561403508</v>
       </c>
       <c r="P4">
         <v>1.69</v>
       </c>
       <c r="Q4">
-        <v>0.05504885993485342</v>
+        <v>0.05633333333333333</v>
       </c>
       <c r="R4">
-        <v>0.599290780141844</v>
+        <v>0.5929824561403508</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,31 +898,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>3.64</v>
+        <v>1.82</v>
       </c>
       <c r="V4">
-        <v>0.1185667752442997</v>
+        <v>0.06066666666666667</v>
       </c>
       <c r="W4">
-        <v>0.09559322033898304</v>
+        <v>0.08456973293768545</v>
       </c>
       <c r="X4">
-        <v>0.08427806289100653</v>
+        <v>0.133594302437083</v>
       </c>
       <c r="Y4">
-        <v>0.01131515744797651</v>
+        <v>-0.04902456949939753</v>
       </c>
       <c r="Z4">
-        <v>1.239300334946036</v>
+        <v>1.214238190286094</v>
       </c>
       <c r="AA4">
-        <v>0.1049497580945292</v>
+        <v>0.09409392801299164</v>
       </c>
       <c r="AB4">
-        <v>0.08427806289100653</v>
+        <v>0.133594302437083</v>
       </c>
       <c r="AC4">
-        <v>0.02067169520352269</v>
+        <v>-0.03950037442409134</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -934,7 +934,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-3.64</v>
+        <v>-1.82</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -943,10 +943,10 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.1345158906134516</v>
+        <v>-0.0645848119233499</v>
       </c>
       <c r="AK4">
-        <v>-0.1210911510312708</v>
+        <v>-0.05708908406524466</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -958,7 +958,129 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>-0.8899755501222495</v>
+        <v>-0.440677966101695</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Jordan</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Al Manara Islamic Insurance Company (ASE:MIIC)</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Insurance (Prop/Cas.)</t>
+        </is>
+      </c>
+      <c r="D5">
+        <v>0.157</v>
+      </c>
+      <c r="G5">
+        <v>0.01937219730941704</v>
+      </c>
+      <c r="H5">
+        <v>0.01937219730941704</v>
+      </c>
+      <c r="I5">
+        <v>0.0484304932735426</v>
+      </c>
+      <c r="J5">
+        <v>0.02994692886822726</v>
+      </c>
+      <c r="K5">
+        <v>0.675</v>
+      </c>
+      <c r="L5">
+        <v>0.03026905829596413</v>
+      </c>
+      <c r="M5">
+        <v>-0</v>
+      </c>
+      <c r="N5">
+        <v>-0</v>
+      </c>
+      <c r="O5">
+        <v>-0</v>
+      </c>
+      <c r="P5">
+        <v>-0</v>
+      </c>
+      <c r="Q5">
+        <v>-0</v>
+      </c>
+      <c r="R5">
+        <v>-0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <v>7.71</v>
+      </c>
+      <c r="V5">
+        <v>2.123966942148761</v>
+      </c>
+      <c r="W5">
+        <v>0.08093525179856116</v>
+      </c>
+      <c r="X5">
+        <v>0.1701540885009717</v>
+      </c>
+      <c r="Y5">
+        <v>-0.08921883670241058</v>
+      </c>
+      <c r="Z5">
+        <v>2.50561797752809</v>
+      </c>
+      <c r="AA5">
+        <v>0.07503556334398516</v>
+      </c>
+      <c r="AB5">
+        <v>0.1444403042140096</v>
+      </c>
+      <c r="AC5">
+        <v>-0.06940474087002442</v>
+      </c>
+      <c r="AD5">
+        <v>1.75</v>
+      </c>
+      <c r="AE5">
+        <v>0</v>
+      </c>
+      <c r="AF5">
+        <v>1.75</v>
+      </c>
+      <c r="AG5">
+        <v>-5.96</v>
+      </c>
+      <c r="AH5">
+        <v>0.3252788104089219</v>
+      </c>
+      <c r="AI5">
+        <v>0.1794871794871795</v>
+      </c>
+      <c r="AJ5">
+        <v>2.55793991416309</v>
+      </c>
+      <c r="AK5">
+        <v>-2.92156862745098</v>
+      </c>
+      <c r="AL5">
+        <v>0</v>
+      </c>
+      <c r="AM5">
+        <v>0</v>
+      </c>
+      <c r="AN5">
+        <v>1.434426229508197</v>
+      </c>
+      <c r="AP5">
+        <v>-4.885245901639344</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/jordan/jordan_insurance_prop_cas.xlsx
+++ b/research/traditional_assets/database/data/jordan/jordan_insurance_prop_cas.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0862</v>
+        <v>0.0401</v>
       </c>
       <c r="E2">
-        <v>-0.00335</v>
+        <v>-0.0217</v>
       </c>
       <c r="G2">
-        <v>0.126090407938258</v>
+        <v>0.18490203396156</v>
       </c>
       <c r="H2">
-        <v>0.126090407938258</v>
+        <v>0.18490203396156</v>
       </c>
       <c r="I2">
-        <v>0.2077618522601984</v>
+        <v>0.203470796790446</v>
       </c>
       <c r="J2">
-        <v>0.1610511286222667</v>
+        <v>0.1766025311252174</v>
       </c>
       <c r="K2">
-        <v>72.52500000000001</v>
+        <v>105.201</v>
       </c>
       <c r="L2">
-        <v>0.159922822491731</v>
+        <v>0.1963071468557567</v>
       </c>
       <c r="M2">
-        <v>20.386</v>
+        <v>3.394</v>
       </c>
       <c r="N2">
-        <v>0.04775021666315322</v>
+        <v>0.005829611817244932</v>
       </c>
       <c r="O2">
-        <v>0.2810892795587728</v>
+        <v>0.03226205074096253</v>
       </c>
       <c r="P2">
-        <v>20.386</v>
+        <v>3.394</v>
       </c>
       <c r="Q2">
-        <v>0.04775021666315322</v>
+        <v>0.005829611817244932</v>
       </c>
       <c r="R2">
-        <v>0.2810892795587728</v>
+        <v>0.03226205074096253</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>256.23</v>
+        <v>120.22</v>
       </c>
       <c r="V2">
-        <v>0.60016864591385</v>
+        <v>0.2064926142219168</v>
       </c>
       <c r="W2">
-        <v>0.08456973293768545</v>
+        <v>0.06587537091988131</v>
       </c>
       <c r="X2">
-        <v>0.133594302437083</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="Y2">
-        <v>-0.04902456949939753</v>
+        <v>-0.04677267592374143</v>
       </c>
       <c r="Z2">
-        <v>2.158906978958393</v>
+        <v>2.857828498293514</v>
       </c>
       <c r="AA2">
-        <v>0.09409392801299164</v>
+        <v>0.06963613550815557</v>
       </c>
       <c r="AB2">
-        <v>0.133594302437083</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AC2">
-        <v>-0.03950037442409134</v>
+        <v>-0.04301191133546717</v>
       </c>
       <c r="AD2">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG2">
-        <v>-254.48</v>
+        <v>-118.42</v>
       </c>
       <c r="AH2">
-        <v>0.004082299150881777</v>
+        <v>0.003082191780821918</v>
       </c>
       <c r="AI2">
-        <v>0.003943661971830986</v>
+        <v>0.003511921020798377</v>
       </c>
       <c r="AJ2">
-        <v>-1.475674108437228</v>
+        <v>-0.2553365820000862</v>
       </c>
       <c r="AK2">
-        <v>-1.357081911262798</v>
+        <v>-0.3018454323001631</v>
       </c>
       <c r="AL2">
-        <v>0.358</v>
+        <v>0</v>
       </c>
       <c r="AM2">
-        <v>0.358</v>
+        <v>0</v>
       </c>
       <c r="AN2">
-        <v>0.01823866597186035</v>
-      </c>
-      <c r="AO2">
-        <v>263.1843575418994</v>
+        <v>0.01619578909483534</v>
       </c>
       <c r="AP2">
-        <v>-2.652214695153726</v>
-      </c>
-      <c r="AQ2">
-        <v>263.1843575418994</v>
+        <v>-1.065502969228001</v>
       </c>
     </row>
     <row r="3">
@@ -722,40 +716,40 @@
         </is>
       </c>
       <c r="G3">
-        <v>0.1335191284519888</v>
+        <v>0.1988824503311258</v>
       </c>
       <c r="H3">
-        <v>0.1335191284519888</v>
+        <v>0.1988824503311258</v>
       </c>
       <c r="I3">
-        <v>0.2259944261464404</v>
+        <v>0.2218543046357616</v>
       </c>
       <c r="J3">
-        <v>0.2235723624974964</v>
+        <v>0.2079183302651398</v>
       </c>
       <c r="K3">
-        <v>69</v>
+        <v>103.9</v>
       </c>
       <c r="L3">
-        <v>0.174816316189511</v>
+        <v>0.2150248344370861</v>
       </c>
       <c r="M3">
-        <v>18.696</v>
+        <v>1.704</v>
       </c>
       <c r="N3">
-        <v>0.04753623188405797</v>
+        <v>0.00310665451230629</v>
       </c>
       <c r="O3">
-        <v>0.2709565217391304</v>
+        <v>0.01640038498556304</v>
       </c>
       <c r="P3">
-        <v>18.696</v>
+        <v>1.704</v>
       </c>
       <c r="Q3">
-        <v>0.04753623188405797</v>
+        <v>0.00310665451230629</v>
       </c>
       <c r="R3">
-        <v>0.2709565217391304</v>
+        <v>0.01640038498556304</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -764,31 +758,31 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>246.7</v>
+        <v>114.8</v>
       </c>
       <c r="V3">
-        <v>0.6272565471650139</v>
+        <v>0.2092980856882407</v>
       </c>
       <c r="W3">
-        <v>0.1744627054361568</v>
+        <v>0.2595553334998751</v>
       </c>
       <c r="X3">
-        <v>0.133594302437083</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="Y3">
-        <v>0.04086840299907379</v>
+        <v>0.1469072866562524</v>
       </c>
       <c r="Z3">
-        <v>2.306838106370543</v>
+        <v>3.145833333333333</v>
       </c>
       <c r="AA3">
-        <v>0.5157452453405134</v>
+        <v>0.6540764139590853</v>
       </c>
       <c r="AB3">
-        <v>0.133594302437083</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AC3">
-        <v>0.3821509429034304</v>
+        <v>0.5414283671154626</v>
       </c>
       <c r="AD3">
         <v>0</v>
@@ -800,7 +794,7 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>-246.7</v>
+        <v>-114.8</v>
       </c>
       <c r="AH3">
         <v>0</v>
@@ -809,28 +803,22 @@
         <v>0</v>
       </c>
       <c r="AJ3">
-        <v>-1.682810368349249</v>
+        <v>-0.2646991007608946</v>
       </c>
       <c r="AK3">
-        <v>-1.606119791666666</v>
+        <v>-0.3231072333239516</v>
       </c>
       <c r="AL3">
-        <v>0.358</v>
+        <v>0</v>
       </c>
       <c r="AM3">
-        <v>0.358</v>
+        <v>0</v>
       </c>
       <c r="AN3">
         <v>0</v>
       </c>
-      <c r="AO3">
-        <v>249.1620111731844</v>
-      </c>
       <c r="AP3">
-        <v>-2.722958057395144</v>
-      </c>
-      <c r="AQ3">
-        <v>249.1620111731844</v>
+        <v>-1.053211009174312</v>
       </c>
     </row>
     <row r="4">
@@ -850,46 +838,46 @@
         </is>
       </c>
       <c r="D4">
-        <v>0.0154</v>
+        <v>0.0272</v>
       </c>
       <c r="E4">
-        <v>-0.00335</v>
+        <v>-0.0217</v>
       </c>
       <c r="G4">
-        <v>0.110958904109589</v>
+        <v>0.09320652173913045</v>
       </c>
       <c r="H4">
-        <v>0.110958904109589</v>
+        <v>0.09320652173913045</v>
       </c>
       <c r="I4">
-        <v>0.107945205479452</v>
+        <v>0.09048913043478261</v>
       </c>
       <c r="J4">
-        <v>0.07749215002932956</v>
+        <v>0.06032608695652174</v>
       </c>
       <c r="K4">
-        <v>2.85</v>
+        <v>2.22</v>
       </c>
       <c r="L4">
-        <v>0.07808219178082192</v>
+        <v>0.06032608695652175</v>
       </c>
       <c r="M4">
         <v>1.69</v>
       </c>
       <c r="N4">
-        <v>0.05633333333333333</v>
+        <v>0.05709459459459459</v>
       </c>
       <c r="O4">
-        <v>0.5929824561403508</v>
+        <v>0.7612612612612611</v>
       </c>
       <c r="P4">
         <v>1.69</v>
       </c>
       <c r="Q4">
-        <v>0.05633333333333333</v>
+        <v>0.05709459459459459</v>
       </c>
       <c r="R4">
-        <v>0.5929824561403508</v>
+        <v>0.7612612612612611</v>
       </c>
       <c r="S4">
         <v>0</v>
@@ -898,31 +886,31 @@
         <v>0</v>
       </c>
       <c r="U4">
-        <v>1.82</v>
+        <v>3.79</v>
       </c>
       <c r="V4">
-        <v>0.06066666666666667</v>
+        <v>0.1280405405405405</v>
       </c>
       <c r="W4">
-        <v>0.08456973293768545</v>
+        <v>0.06587537091988131</v>
       </c>
       <c r="X4">
-        <v>0.133594302437083</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="Y4">
-        <v>-0.04902456949939753</v>
+        <v>-0.04677267592374143</v>
       </c>
       <c r="Z4">
-        <v>1.214238190286094</v>
+        <v>1.154328732747804</v>
       </c>
       <c r="AA4">
-        <v>0.09409392801299164</v>
+        <v>0.06963613550815557</v>
       </c>
       <c r="AB4">
-        <v>0.133594302437083</v>
+        <v>0.1126480468436227</v>
       </c>
       <c r="AC4">
-        <v>-0.03950037442409134</v>
+        <v>-0.04301191133546717</v>
       </c>
       <c r="AD4">
         <v>0</v>
@@ -934,7 +922,7 @@
         <v>0</v>
       </c>
       <c r="AG4">
-        <v>-1.82</v>
+        <v>-3.79</v>
       </c>
       <c r="AH4">
         <v>0</v>
@@ -943,10 +931,10 @@
         <v>0</v>
       </c>
       <c r="AJ4">
-        <v>-0.0645848119233499</v>
+        <v>-0.1468423091824874</v>
       </c>
       <c r="AK4">
-        <v>-0.05708908406524466</v>
+        <v>-0.1262912362545818</v>
       </c>
       <c r="AL4">
         <v>0</v>
@@ -958,7 +946,7 @@
         <v>0</v>
       </c>
       <c r="AP4">
-        <v>-0.440677966101695</v>
+        <v>-1.095375722543353</v>
       </c>
     </row>
     <row r="5">
@@ -978,25 +966,25 @@
         </is>
       </c>
       <c r="D5">
-        <v>0.157</v>
+        <v>0.053</v>
       </c>
       <c r="G5">
-        <v>0.01937219730941704</v>
+        <v>-0.02773584905660377</v>
       </c>
       <c r="H5">
-        <v>0.01937219730941704</v>
+        <v>-0.02773584905660377</v>
       </c>
       <c r="I5">
-        <v>0.0484304932735426</v>
+        <v>-0.09371069182389936</v>
       </c>
       <c r="J5">
-        <v>0.02994692886822726</v>
+        <v>-0.09371069182389936</v>
       </c>
       <c r="K5">
-        <v>0.675</v>
+        <v>-0.919</v>
       </c>
       <c r="L5">
-        <v>0.03026905829596413</v>
+        <v>-0.05779874213836478</v>
       </c>
       <c r="M5">
         <v>-0</v>
@@ -1005,7 +993,7 @@
         <v>-0</v>
       </c>
       <c r="O5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="P5">
         <v>-0</v>
@@ -1014,61 +1002,61 @@
         <v>-0</v>
       </c>
       <c r="R5">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="S5">
         <v>0</v>
       </c>
       <c r="U5">
-        <v>7.71</v>
+        <v>1.63</v>
       </c>
       <c r="V5">
-        <v>2.123966942148761</v>
+        <v>0.3975609756097561</v>
       </c>
       <c r="W5">
-        <v>0.08093525179856116</v>
+        <v>-0.114875</v>
       </c>
       <c r="X5">
-        <v>0.1701540885009717</v>
+        <v>0.1385849218326024</v>
       </c>
       <c r="Y5">
-        <v>-0.08921883670241058</v>
+        <v>-0.2534599218326025</v>
       </c>
       <c r="Z5">
-        <v>2.50561797752809</v>
+        <v>7.794117647058823</v>
       </c>
       <c r="AA5">
-        <v>0.07503556334398516</v>
+        <v>-0.7303921568627451</v>
       </c>
       <c r="AB5">
-        <v>0.1444403042140096</v>
+        <v>0.1213376165473249</v>
       </c>
       <c r="AC5">
-        <v>-0.06940474087002442</v>
+        <v>-0.8517297734100699</v>
       </c>
       <c r="AD5">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AE5">
         <v>0</v>
       </c>
       <c r="AF5">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AG5">
-        <v>-5.96</v>
+        <v>0.1700000000000002</v>
       </c>
       <c r="AH5">
-        <v>0.3252788104089219</v>
+        <v>0.3050847457627119</v>
       </c>
       <c r="AI5">
-        <v>0.1794871794871795</v>
+        <v>0.2083333333333333</v>
       </c>
       <c r="AJ5">
-        <v>2.55793991416309</v>
+        <v>0.03981264637002346</v>
       </c>
       <c r="AK5">
-        <v>-2.92156862745098</v>
+        <v>0.02425106990014268</v>
       </c>
       <c r="AL5">
         <v>0</v>
@@ -1077,10 +1065,10 @@
         <v>0</v>
       </c>
       <c r="AN5">
-        <v>1.434426229508197</v>
+        <v>-1.363636363636364</v>
       </c>
       <c r="AP5">
-        <v>-4.885245901639344</v>
+        <v>-0.1287878787878789</v>
       </c>
     </row>
   </sheetData>
